--- a/tiflow-chargeitem/develop/2.0.0-ballot.2/ValueSet-tiflow-chargeitem-operation-outcome-details-vs.xlsx
+++ b/tiflow-chargeitem/develop/2.0.0-ballot.2/ValueSet-tiflow-chargeitem-operation-outcome-details-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
